--- a/STUDIO/org.openl.rules.test/test-resources/functionality/EPBDS-13565_Access_to_table_properties/propertyAccessTest-AK.xlsx
+++ b/STUDIO/org.openl.rules.test/test-resources/functionality/EPBDS-13565_Access_to_table_properties/propertyAccessTest-AK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="171">
   <si>
     <t>Datatype SpreadsheetProperties</t>
   </si>
@@ -46,9 +46,6 @@
     <t>caRegions</t>
   </si>
   <si>
-    <t>cacheable</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -211,15 +208,6 @@
     <t>=$dispatchingProperties.caRegions[1]</t>
   </si>
   <si>
-    <t>Cacheable</t>
-  </si>
-  <si>
-    <t>=$properties.cacheable</t>
-  </si>
-  <si>
-    <t>=$dispatchingProperties.cacheable[1]</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -403,10 +391,10 @@
     <t>ReturnObject</t>
   </si>
   <si>
-    <t>=SpreadsheetProperties($Properties$CalculateAllCells, $Properties$AutoType, $Properties$TableStructureDetails, $Properties$BuildPhase, $Properties$CaProvinces, $Properties$CaRegions, $Properties$Cacheable, $Properties$Category, $Properties$Country, $Properties$Currency, $Properties$Description, $Properties$EffectiveDate, setTime($Properties$EndRequestDate,0,0,0,0), setTime($Properties$ExpirationDate,0,0,0,0), $Properties$Id, $Properties$Lang, $Properties$Lob, $Properties$Nature, $Properties$Origin, $Properties$Parallel, $Properties$Region, $Properties$StartRequestDate, $Properties$State, $Properties$Tags, $Properties$Usregion, $Properties$Version, $Properties$Active)</t>
-  </si>
-  <si>
-    <t>=SpreadsheetProperties($DispatchingProperties$CalculateAllCells, $DispatchingProperties$AutoType, $DispatchingProperties$TableStructureDetails, $DispatchingProperties$BuildPhase, $DispatchingProperties$CaProvinces, $DispatchingProperties$CaRegions, $DispatchingProperties$Cacheable, $DispatchingProperties$Category, $DispatchingProperties$Country, $DispatchingProperties$Currency, $DispatchingProperties$Description, $DispatchingProperties$EffectiveDate, setTime($DispatchingProperties$EndRequestDate,0,0,0,0), setTime($DispatchingProperties$ExpirationDate,0,0,0,0), $DispatchingProperties$Id, $DispatchingProperties$Lang, $DispatchingProperties$Lob, $DispatchingProperties$Nature, $DispatchingProperties$Origin, $DispatchingProperties$Parallel, $DispatchingProperties$Region, $DispatchingProperties$StartRequestDate, $DispatchingProperties$State, $DispatchingProperties$Tags, $DispatchingProperties$Usregion, $DispatchingProperties$Version, $DispatchingProperties$Active)</t>
+    <t>=SpreadsheetProperties($Properties$CalculateAllCells, $Properties$AutoType, $Properties$TableStructureDetails, $Properties$BuildPhase, $Properties$CaProvinces, $Properties$CaRegions, $Properties$Category, $Properties$Country, $Properties$Currency, $Properties$Description, $Properties$EffectiveDate, setTime($Properties$EndRequestDate,0,0,0,0), setTime($Properties$ExpirationDate,0,0,0,0), $Properties$Id, $Properties$Lang, $Properties$Lob, $Properties$Nature, $Properties$Origin, $Properties$Parallel, $Properties$Region, $Properties$StartRequestDate, $Properties$State, $Properties$Tags, $Properties$Usregion, $Properties$Version, $Properties$Active)</t>
+  </si>
+  <si>
+    <t>=SpreadsheetProperties($DispatchingProperties$CalculateAllCells, $DispatchingProperties$AutoType, $DispatchingProperties$TableStructureDetails, $DispatchingProperties$BuildPhase, $DispatchingProperties$CaProvinces, $DispatchingProperties$CaRegions, $DispatchingProperties$Category, $DispatchingProperties$Country, $DispatchingProperties$Currency, $DispatchingProperties$Description, $DispatchingProperties$EffectiveDate, setTime($DispatchingProperties$EndRequestDate,0,0,0,0), setTime($DispatchingProperties$ExpirationDate,0,0,0,0), $DispatchingProperties$Id, $DispatchingProperties$Lang, $DispatchingProperties$Lob, $DispatchingProperties$Nature, $DispatchingProperties$Origin, $DispatchingProperties$Parallel, $DispatchingProperties$Region, $DispatchingProperties$StartRequestDate, $DispatchingProperties$State, $DispatchingProperties$Tags, $DispatchingProperties$Usregion, $DispatchingProperties$Version, $DispatchingProperties$Active)</t>
   </si>
   <si>
     <t xml:space="preserve">Datatype RulesProperties </t>
@@ -415,9 +403,6 @@
     <t>failOnMissLocal</t>
   </si>
   <si>
-    <t>cacheableLocal</t>
-  </si>
-  <si>
     <t>DTEmptyResultProcessingEnum</t>
   </si>
   <si>
@@ -448,9 +433,6 @@
     <t>failOnMissOtherTable</t>
   </si>
   <si>
-    <t>cacheableOtherTable</t>
-  </si>
-  <si>
     <t>emptyResultProcessingOtherTable</t>
   </si>
   <si>
@@ -475,9 +457,6 @@
     <t>failOnMissOtherModule</t>
   </si>
   <si>
-    <t>cacheableOtherModule</t>
-  </si>
-  <si>
     <t>emptyResultProcessingOtherModule</t>
   </si>
   <si>
@@ -532,7 +511,7 @@
     <t>someParam</t>
   </si>
   <si>
-    <t>new RulesProperties($properties.failOnMiss, $properties.cacheable, $properties.emptyResultProcessing, $properties.parallel, $properties.validateDT, $properties.buildPhase, $properties.id, $properties.state, $properties.effectiveDate,$dispatchingProperties[1].failOnMiss, $dispatchingProperties[1].cacheable, $dispatchingProperties[1].emptyResultProcessing, $dispatchingProperties[1].parallel, $dispatchingProperties[1].validateDT, $dispatchingProperties[1].buildPhase, $dispatchingProperties[1].id, $dispatchingProperties[1].state, $dispatchingProperties[1].effectiveDate,$dispatchingProperties[0].failOnMiss, $dispatchingProperties[0].cacheable, $dispatchingProperties[0].emptyResultProcessing, $dispatchingProperties[0].parallel, $dispatchingProperties[0].validateDT, $dispatchingProperties[0].buildPhase, $dispatchingProperties[0].id, $dispatchingProperties[0].state, $dispatchingProperties[0].effectiveDate)</t>
+    <t>new RulesProperties($properties.failOnMiss, $properties.emptyResultProcessing, $properties.parallel, $properties.validateDT, $properties.buildPhase, $properties.id, $properties.state, $properties.effectiveDate,$dispatchingProperties[1].failOnMiss, $dispatchingProperties[1].emptyResultProcessing, $dispatchingProperties[1].parallel, $dispatchingProperties[1].validateDT, $dispatchingProperties[1].buildPhase, $dispatchingProperties[1].id, $dispatchingProperties[1].state, $dispatchingProperties[1].effectiveDate,$dispatchingProperties[0].failOnMiss, $dispatchingProperties[0].emptyResultProcessing, $dispatchingProperties[0].parallel, $dispatchingProperties[0].validateDT, $dispatchingProperties[0].buildPhase, $dispatchingProperties[0].id, $dispatchingProperties[0].state, $dispatchingProperties[0].effectiveDate)</t>
   </si>
   <si>
     <t>Integer</t>
@@ -572,7 +551,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color indexed="14"/>
+      <color indexed="9"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -585,7 +564,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -630,28 +609,28 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -660,16 +639,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -704,13 +683,13 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -731,16 +710,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -775,10 +754,10 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -798,91 +777,91 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="7" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -902,12 +881,12 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ffcfcfcf"/>
       <rgbColor rgb="ffd8d8d8"/>
       <rgbColor rgb="ff8eaadb"/>
       <rgbColor rgb="fffff2cb"/>
-      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1106,17 +1085,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1144,10 +1123,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1395,12 +1374,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1687,7 +1666,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1715,10 +1694,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1969,7 +1948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="16" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.8516" style="1" customWidth="1"/>
@@ -2086,7 +2065,7 @@
     <row r="12" ht="15.35" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" t="s" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s" s="9">
         <v>11</v>
@@ -2097,10 +2076,10 @@
     <row r="13" ht="15.35" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" t="s" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s" s="9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="2"/>
@@ -2108,10 +2087,10 @@
     <row r="14" ht="15.35" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" t="s" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="2"/>
@@ -2119,7 +2098,7 @@
     <row r="15" ht="15.35" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" t="s" s="8">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s" s="9">
         <v>16</v>
@@ -2130,10 +2109,10 @@
     <row r="16" ht="15.35" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" t="s" s="8">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s" s="9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="2"/>
@@ -2141,7 +2120,7 @@
     <row r="17" ht="15.35" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" t="s" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s" s="9">
         <v>19</v>
@@ -2152,7 +2131,7 @@
     <row r="18" ht="15.35" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" t="s" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s" s="9">
         <v>20</v>
@@ -2163,7 +2142,7 @@
     <row r="19" ht="15.35" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" t="s" s="8">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s" s="9">
         <v>21</v>
@@ -2174,10 +2153,10 @@
     <row r="20" ht="15.35" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" t="s" s="8">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s" s="9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="2"/>
@@ -2185,10 +2164,10 @@
     <row r="21" ht="15.35" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" t="s" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="2"/>
@@ -2196,7 +2175,7 @@
     <row r="22" ht="15.35" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" t="s" s="8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s" s="9">
         <v>26</v>
@@ -2207,10 +2186,10 @@
     <row r="23" ht="15.35" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" t="s" s="8">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="2"/>
@@ -2218,7 +2197,7 @@
     <row r="24" ht="15.35" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" t="s" s="8">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s" s="9">
         <v>29</v>
@@ -2229,10 +2208,10 @@
     <row r="25" ht="15.35" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" t="s" s="8">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="2"/>
@@ -2240,7 +2219,7 @@
     <row r="26" ht="15.35" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" t="s" s="8">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s" s="9">
         <v>32</v>
@@ -2251,18 +2230,18 @@
     <row r="27" ht="15.35" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" t="s" s="8">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" ht="15.35" customHeight="1">
+    <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" t="s" s="8">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s" s="9">
         <v>35</v>
@@ -2270,13 +2249,13 @@
       <c r="D28" s="7"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" ht="21" customHeight="1">
+    <row r="29" ht="15.35" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" t="s" s="8">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s" s="9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="2"/>
@@ -2284,7 +2263,7 @@
     <row r="30" ht="15.35" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" t="s" s="8">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s" s="9">
         <v>38</v>
@@ -2295,7 +2274,7 @@
     <row r="31" ht="15.35" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" t="s" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s" s="9">
         <v>39</v>
@@ -2304,53 +2283,53 @@
       <c r="E31" s="2"/>
     </row>
     <row r="32" ht="15.35" customHeight="1">
-      <c r="A32" s="4"/>
-      <c r="B32" t="s" s="8">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s" s="9">
-        <v>40</v>
-      </c>
-      <c r="D32" s="7"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" ht="15.35" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
     <row r="34" ht="15.35" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" ht="15.35" customHeight="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="2"/>
+      <c r="A35" s="4"/>
+      <c r="B35" t="s" s="9">
+        <v>40</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" ht="15.35" customHeight="1">
       <c r="A36" s="4"/>
-      <c r="B36" t="s" s="9">
+      <c r="B36" t="s" s="12">
         <v>41</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
+      <c r="C36" t="s" s="13">
+        <v>21</v>
+      </c>
+      <c r="D36" t="s" s="13">
+        <v>42</v>
+      </c>
       <c r="E36" s="7"/>
     </row>
     <row r="37" ht="15.35" customHeight="1">
       <c r="A37" s="4"/>
-      <c r="B37" t="s" s="12">
-        <v>42</v>
-      </c>
+      <c r="B37" s="14"/>
       <c r="C37" t="s" s="13">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s" s="13">
         <v>43</v>
@@ -2359,419 +2338,417 @@
     </row>
     <row r="38" ht="15.35" customHeight="1">
       <c r="A38" s="4"/>
-      <c r="B38" s="14"/>
-      <c r="C38" t="s" s="13">
-        <v>39</v>
-      </c>
-      <c r="D38" t="s" s="13">
+      <c r="B38" t="s" s="15">
         <v>44</v>
+      </c>
+      <c r="C38" t="s" s="15">
+        <v>45</v>
+      </c>
+      <c r="D38" t="s" s="15">
+        <v>46</v>
       </c>
       <c r="E38" s="7"/>
     </row>
     <row r="39" ht="15.35" customHeight="1">
       <c r="A39" s="4"/>
-      <c r="B39" t="s" s="15">
-        <v>45</v>
-      </c>
-      <c r="C39" t="s" s="15">
-        <v>46</v>
-      </c>
-      <c r="D39" t="s" s="15">
+      <c r="B39" t="s" s="16">
         <v>47</v>
+      </c>
+      <c r="C39" t="s" s="9">
+        <v>48</v>
+      </c>
+      <c r="D39" t="s" s="9">
+        <v>49</v>
       </c>
       <c r="E39" s="7"/>
     </row>
     <row r="40" ht="15.35" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" t="s" s="16">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s" s="9">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D40" t="s" s="9">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E40" s="7"/>
     </row>
     <row r="41" ht="15.35" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" t="s" s="16">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s" s="9">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D41" t="s" s="9">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E41" s="7"/>
     </row>
     <row r="42" ht="15.35" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" t="s" s="16">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s" s="9">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s" s="9">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E42" s="7"/>
     </row>
     <row r="43" ht="15.35" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" t="s" s="16">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s" s="9">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s" s="9">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E43" s="7"/>
     </row>
     <row r="44" ht="15.35" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" t="s" s="16">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s" s="9">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E44" s="7"/>
     </row>
     <row r="45" ht="15.35" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" t="s" s="16">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s" s="9">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D45" t="s" s="9">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E45" s="7"/>
     </row>
     <row r="46" ht="15.35" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" t="s" s="16">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s" s="9">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s" s="9">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E46" s="7"/>
     </row>
     <row r="47" ht="15.35" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" t="s" s="16">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C47" t="s" s="9">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s" s="9">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E47" s="7"/>
     </row>
     <row r="48" ht="15.35" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" t="s" s="16">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C48" t="s" s="9">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s" s="9">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E48" s="7"/>
     </row>
     <row r="49" ht="15.35" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" t="s" s="16">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s" s="9">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D49" t="s" s="9">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E49" s="7"/>
     </row>
     <row r="50" ht="15.35" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" t="s" s="16">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C50" t="s" s="9">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s" s="9">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E50" s="7"/>
     </row>
     <row r="51" ht="15.35" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" t="s" s="16">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s" s="9">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D51" t="s" s="9">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E51" s="7"/>
     </row>
     <row r="52" ht="15.35" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" t="s" s="16">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C52" t="s" s="9">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D52" t="s" s="9">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E52" s="7"/>
     </row>
     <row r="53" ht="15.35" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" t="s" s="16">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s" s="9">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D53" t="s" s="9">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E53" s="7"/>
     </row>
     <row r="54" ht="15.35" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" t="s" s="16">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s" s="9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D54" t="s" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E54" s="7"/>
     </row>
     <row r="55" ht="15.35" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" t="s" s="16">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s" s="9">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s" s="9">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E55" s="7"/>
     </row>
     <row r="56" ht="15.35" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" t="s" s="16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s" s="9">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D56" t="s" s="9">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E56" s="7"/>
     </row>
     <row r="57" ht="15.35" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" t="s" s="16">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s" s="9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s" s="9">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E57" s="7"/>
     </row>
     <row r="58" ht="15.35" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" t="s" s="16">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s" s="9">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D58" t="s" s="9">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E58" s="7"/>
     </row>
     <row r="59" ht="15.35" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" t="s" s="16">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C59" t="s" s="9">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D59" t="s" s="9">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E59" s="7"/>
     </row>
     <row r="60" ht="15.35" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" t="s" s="16">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C60" t="s" s="9">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D60" t="s" s="9">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E60" s="7"/>
     </row>
     <row r="61" ht="15.35" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" t="s" s="16">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s" s="9">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s" s="9">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E61" s="7"/>
     </row>
     <row r="62" ht="15.35" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" t="s" s="16">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s" s="9">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D62" t="s" s="9">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E62" s="7"/>
     </row>
     <row r="63" ht="15.35" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" t="s" s="16">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C63" t="s" s="9">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D63" t="s" s="9">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E63" s="7"/>
     </row>
     <row r="64" ht="15.35" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" t="s" s="16">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C64" t="s" s="9">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s" s="9">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E64" s="7"/>
     </row>
-    <row r="65" ht="15.35" customHeight="1">
+    <row r="65" ht="204" customHeight="1">
       <c r="A65" s="4"/>
-      <c r="B65" t="s" s="16">
-        <v>123</v>
+      <c r="B65" t="s" s="9">
+        <v>125</v>
       </c>
       <c r="C65" t="s" s="9">
-        <v>124</v>
-      </c>
-      <c r="D65" t="s" s="9">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="D65" t="s" s="17">
+        <v>127</v>
       </c>
       <c r="E65" s="7"/>
     </row>
     <row r="66" ht="15.35" customHeight="1">
-      <c r="A66" s="4"/>
-      <c r="B66" t="s" s="16">
-        <v>126</v>
-      </c>
-      <c r="C66" t="s" s="9">
-        <v>127</v>
-      </c>
-      <c r="D66" t="s" s="9">
-        <v>128</v>
-      </c>
-      <c r="E66" s="7"/>
-    </row>
-    <row r="67" ht="204" customHeight="1">
-      <c r="A67" s="4"/>
-      <c r="B67" t="s" s="9">
-        <v>129</v>
-      </c>
-      <c r="C67" t="s" s="9">
-        <v>130</v>
-      </c>
-      <c r="D67" t="s" s="17">
-        <v>131</v>
-      </c>
-      <c r="E67" s="7"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" ht="15.35" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
     </row>
     <row r="68" ht="15.35" customHeight="1">
       <c r="A68" s="2"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="2"/>
       <c r="E68" s="2"/>
     </row>
     <row r="69" ht="15.35" customHeight="1">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+      <c r="A69" s="4"/>
+      <c r="B69" t="s" s="18">
+        <v>128</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="7"/>
       <c r="E69" s="2"/>
     </row>
     <row r="70" ht="15.35" customHeight="1">
-      <c r="A70" s="2"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="2"/>
+      <c r="A70" s="4"/>
+      <c r="B70" t="s" s="9">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s" s="9">
+        <v>129</v>
+      </c>
+      <c r="D70" s="7"/>
       <c r="E70" s="2"/>
     </row>
     <row r="71" ht="15.35" customHeight="1">
       <c r="A71" s="4"/>
-      <c r="B71" t="s" s="18">
-        <v>132</v>
-      </c>
-      <c r="C71" s="19"/>
+      <c r="B71" t="s" s="9">
+        <v>130</v>
+      </c>
+      <c r="C71" t="s" s="9">
+        <v>131</v>
+      </c>
       <c r="D71" s="7"/>
       <c r="E71" s="2"/>
     </row>
@@ -2781,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s" s="9">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D72" s="7"/>
       <c r="E72" s="2"/>
@@ -2789,7 +2766,7 @@
     <row r="73" ht="15.35" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" t="s" s="9">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="C73" t="s" s="9">
         <v>134</v>
@@ -2800,10 +2777,10 @@
     <row r="74" ht="15.35" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" t="s" s="9">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s" s="9">
         <v>135</v>
-      </c>
-      <c r="C74" t="s" s="9">
-        <v>136</v>
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="2"/>
@@ -2811,10 +2788,10 @@
     <row r="75" ht="15.35" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" t="s" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C75" t="s" s="9">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D75" s="7"/>
       <c r="E75" s="2"/>
@@ -2822,10 +2799,10 @@
     <row r="76" ht="15.35" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" t="s" s="9">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="C76" t="s" s="9">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D76" s="7"/>
       <c r="E76" s="2"/>
@@ -2833,10 +2810,10 @@
     <row r="77" ht="15.35" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" t="s" s="9">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s" s="9">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D77" s="7"/>
       <c r="E77" s="2"/>
@@ -2844,10 +2821,10 @@
     <row r="78" ht="15.35" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" t="s" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s" s="9">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D78" s="7"/>
       <c r="E78" s="2"/>
@@ -2855,10 +2832,10 @@
     <row r="79" ht="15.35" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" t="s" s="9">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="C79" t="s" s="9">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D79" s="7"/>
       <c r="E79" s="2"/>
@@ -2866,10 +2843,10 @@
     <row r="80" ht="15.35" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" t="s" s="9">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C80" t="s" s="9">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D80" s="7"/>
       <c r="E80" s="2"/>
@@ -2877,10 +2854,10 @@
     <row r="81" ht="15.35" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" t="s" s="9">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="C81" t="s" s="9">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="2"/>
@@ -2888,10 +2865,10 @@
     <row r="82" ht="15.35" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" t="s" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C82" t="s" s="9">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="2"/>
@@ -2899,10 +2876,10 @@
     <row r="83" ht="15.35" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" t="s" s="9">
-        <v>135</v>
+        <v>5</v>
       </c>
       <c r="C83" t="s" s="9">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="2"/>
@@ -2910,10 +2887,10 @@
     <row r="84" ht="15.35" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" t="s" s="9">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C84" t="s" s="9">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="2"/>
@@ -2921,10 +2898,10 @@
     <row r="85" ht="15.35" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" t="s" s="9">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s" s="9">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D85" s="7"/>
       <c r="E85" s="2"/>
@@ -2932,10 +2909,10 @@
     <row r="86" ht="15.35" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" t="s" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C86" t="s" s="9">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D86" s="7"/>
       <c r="E86" s="2"/>
@@ -2943,10 +2920,10 @@
     <row r="87" ht="15.35" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" t="s" s="9">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="C87" t="s" s="9">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D87" s="7"/>
       <c r="E87" s="2"/>
@@ -2954,10 +2931,10 @@
     <row r="88" ht="15.35" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" t="s" s="9">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C88" t="s" s="9">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D88" s="7"/>
       <c r="E88" s="2"/>
@@ -2965,10 +2942,10 @@
     <row r="89" ht="15.35" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" t="s" s="9">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="C89" t="s" s="9">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="2"/>
@@ -2976,10 +2953,10 @@
     <row r="90" ht="15.35" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" t="s" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C90" t="s" s="9">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="2"/>
@@ -2987,10 +2964,10 @@
     <row r="91" ht="15.35" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" t="s" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C91" t="s" s="9">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="2"/>
@@ -2998,10 +2975,10 @@
     <row r="92" ht="15.35" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" t="s" s="9">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="C92" t="s" s="9">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="2"/>
@@ -3009,123 +2986,123 @@
     <row r="93" ht="15.35" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" t="s" s="9">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C93" t="s" s="9">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="2"/>
     </row>
     <row r="94" ht="15.35" customHeight="1">
-      <c r="A94" s="4"/>
-      <c r="B94" t="s" s="9">
-        <v>138</v>
-      </c>
-      <c r="C94" t="s" s="9">
+      <c r="A94" s="2"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" ht="15.35" customHeight="1">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" ht="15.35" customHeight="1">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" ht="15.35" customHeight="1">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" ht="15.35" customHeight="1">
+      <c r="A98" s="2"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" ht="15.35" customHeight="1">
+      <c r="A99" s="4"/>
+      <c r="B99" t="s" s="20">
+        <v>155</v>
+      </c>
+      <c r="C99" s="21"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" ht="15.35" customHeight="1">
+      <c r="A100" s="4"/>
+      <c r="B100" t="s" s="22">
+        <v>41</v>
+      </c>
+      <c r="C100" t="s" s="13">
+        <v>18</v>
+      </c>
+      <c r="D100" s="23">
+        <v>45240</v>
+      </c>
+      <c r="E100" s="7"/>
+    </row>
+    <row r="101" ht="15.35" customHeight="1">
+      <c r="A101" s="4"/>
+      <c r="B101" s="24"/>
+      <c r="C101" t="s" s="13">
+        <v>156</v>
+      </c>
+      <c r="D101" t="b" s="25">
+        <v>0</v>
+      </c>
+      <c r="E101" s="7"/>
+    </row>
+    <row r="102" ht="15.35" customHeight="1">
+      <c r="A102" s="4"/>
+      <c r="B102" s="11"/>
+      <c r="C102" t="s" s="13">
         <v>157</v>
       </c>
-      <c r="D94" s="7"/>
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" ht="15.35" customHeight="1">
-      <c r="A95" s="4"/>
-      <c r="B95" t="s" s="9">
-        <v>5</v>
-      </c>
-      <c r="C95" t="s" s="9">
+      <c r="D102" t="s" s="13">
         <v>158</v>
       </c>
-      <c r="D95" s="7"/>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" ht="15.35" customHeight="1">
-      <c r="A96" s="4"/>
-      <c r="B96" t="s" s="9">
-        <v>5</v>
-      </c>
-      <c r="C96" t="s" s="9">
-        <v>159</v>
-      </c>
-      <c r="D96" s="7"/>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" ht="15.35" customHeight="1">
-      <c r="A97" s="4"/>
-      <c r="B97" t="s" s="9">
-        <v>34</v>
-      </c>
-      <c r="C97" t="s" s="9">
-        <v>160</v>
-      </c>
-      <c r="D97" s="7"/>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" ht="15.35" customHeight="1">
-      <c r="A98" s="4"/>
-      <c r="B98" t="s" s="9">
-        <v>18</v>
-      </c>
-      <c r="C98" t="s" s="9">
-        <v>161</v>
-      </c>
-      <c r="D98" s="7"/>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" ht="15.35" customHeight="1">
-      <c r="A99" s="2"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100" ht="15.35" customHeight="1">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101" ht="15.35" customHeight="1">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102" ht="15.35" customHeight="1">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
+      <c r="E102" s="7"/>
     </row>
     <row r="103" ht="15.35" customHeight="1">
-      <c r="A103" s="2"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
+      <c r="A103" s="4"/>
+      <c r="B103" s="24"/>
+      <c r="C103" t="s" s="13">
+        <v>29</v>
+      </c>
+      <c r="D103" t="b" s="25">
+        <v>0</v>
+      </c>
+      <c r="E103" s="7"/>
     </row>
     <row r="104" ht="15.35" customHeight="1">
       <c r="A104" s="4"/>
-      <c r="B104" t="s" s="20">
-        <v>162</v>
-      </c>
-      <c r="C104" s="21"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="2"/>
+      <c r="B104" s="24"/>
+      <c r="C104" t="s" s="13">
+        <v>159</v>
+      </c>
+      <c r="D104" t="s" s="13">
+        <v>160</v>
+      </c>
+      <c r="E104" s="7"/>
     </row>
     <row r="105" ht="15.35" customHeight="1">
       <c r="A105" s="4"/>
-      <c r="B105" t="s" s="22">
-        <v>42</v>
-      </c>
+      <c r="B105" s="24"/>
       <c r="C105" t="s" s="13">
-        <v>19</v>
-      </c>
-      <c r="D105" s="23">
-        <v>45240</v>
+        <v>6</v>
+      </c>
+      <c r="D105" t="s" s="13">
+        <v>161</v>
       </c>
       <c r="E105" s="7"/>
     </row>
@@ -3133,169 +3110,103 @@
       <c r="A106" s="4"/>
       <c r="B106" s="24"/>
       <c r="C106" t="s" s="13">
-        <v>163</v>
-      </c>
-      <c r="D106" t="b" s="25">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="D106" t="s" s="13">
+        <v>162</v>
       </c>
       <c r="E106" s="7"/>
     </row>
     <row r="107" ht="15.35" customHeight="1">
       <c r="A107" s="4"/>
-      <c r="B107" s="24"/>
-      <c r="C107" t="s" s="13">
-        <v>11</v>
-      </c>
-      <c r="D107" t="b" s="25">
-        <v>1</v>
-      </c>
+      <c r="B107" t="s" s="9">
+        <v>163</v>
+      </c>
+      <c r="C107" t="s" s="9">
+        <v>164</v>
+      </c>
+      <c r="D107" s="11"/>
       <c r="E107" s="7"/>
     </row>
-    <row r="108" ht="15.35" customHeight="1">
+    <row r="108" ht="105.35" customHeight="1">
       <c r="A108" s="4"/>
-      <c r="B108" s="11"/>
-      <c r="C108" t="s" s="13">
-        <v>164</v>
-      </c>
-      <c r="D108" t="s" s="13">
+      <c r="B108" t="s" s="9">
         <v>165</v>
       </c>
+      <c r="C108" t="s" s="26">
+        <v>166</v>
+      </c>
+      <c r="D108" s="27"/>
       <c r="E108" s="7"/>
     </row>
     <row r="109" ht="15.35" customHeight="1">
       <c r="A109" s="4"/>
-      <c r="B109" s="24"/>
-      <c r="C109" t="s" s="13">
-        <v>30</v>
-      </c>
-      <c r="D109" t="b" s="25">
-        <v>0</v>
-      </c>
+      <c r="B109" t="s" s="9">
+        <v>167</v>
+      </c>
+      <c r="C109" t="s" s="9">
+        <v>168</v>
+      </c>
+      <c r="D109" s="11"/>
       <c r="E109" s="7"/>
     </row>
     <row r="110" ht="15.35" customHeight="1">
       <c r="A110" s="4"/>
-      <c r="B110" s="24"/>
-      <c r="C110" t="s" s="13">
-        <v>166</v>
-      </c>
-      <c r="D110" t="s" s="13">
-        <v>167</v>
-      </c>
+      <c r="B110" t="s" s="9">
+        <v>169</v>
+      </c>
+      <c r="C110" t="s" s="9">
+        <v>170</v>
+      </c>
+      <c r="D110" s="11"/>
       <c r="E110" s="7"/>
     </row>
     <row r="111" ht="15.35" customHeight="1">
       <c r="A111" s="4"/>
-      <c r="B111" s="24"/>
-      <c r="C111" t="s" s="13">
-        <v>6</v>
-      </c>
-      <c r="D111" t="s" s="13">
-        <v>168</v>
-      </c>
+      <c r="B111" s="28">
+        <v>1</v>
+      </c>
+      <c r="C111" s="29">
+        <v>100</v>
+      </c>
+      <c r="D111" s="30"/>
       <c r="E111" s="7"/>
     </row>
     <row r="112" ht="15.35" customHeight="1">
       <c r="A112" s="4"/>
-      <c r="B112" s="24"/>
-      <c r="C112" t="s" s="13">
-        <v>22</v>
-      </c>
-      <c r="D112" t="s" s="13">
-        <v>169</v>
-      </c>
+      <c r="B112" s="28">
+        <v>2</v>
+      </c>
+      <c r="C112" s="29">
+        <v>200</v>
+      </c>
+      <c r="D112" s="30"/>
       <c r="E112" s="7"/>
     </row>
     <row r="113" ht="15.35" customHeight="1">
       <c r="A113" s="4"/>
-      <c r="B113" t="s" s="9">
-        <v>170</v>
-      </c>
-      <c r="C113" t="s" s="9">
-        <v>171</v>
+      <c r="B113" s="28">
+        <v>3</v>
+      </c>
+      <c r="C113" s="28">
+        <v>300</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="7"/>
-    </row>
-    <row r="114" ht="162" customHeight="1">
-      <c r="A114" s="4"/>
-      <c r="B114" t="s" s="9">
-        <v>172</v>
-      </c>
-      <c r="C114" t="s" s="26">
-        <v>173</v>
-      </c>
-      <c r="D114" s="27"/>
-      <c r="E114" s="7"/>
-    </row>
-    <row r="115" ht="15.35" customHeight="1">
-      <c r="A115" s="4"/>
-      <c r="B115" t="s" s="9">
-        <v>174</v>
-      </c>
-      <c r="C115" t="s" s="9">
-        <v>175</v>
-      </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="7"/>
-    </row>
-    <row r="116" ht="15.35" customHeight="1">
-      <c r="A116" s="4"/>
-      <c r="B116" t="s" s="9">
-        <v>176</v>
-      </c>
-      <c r="C116" t="s" s="9">
-        <v>177</v>
-      </c>
-      <c r="D116" s="11"/>
-      <c r="E116" s="7"/>
-    </row>
-    <row r="117" ht="15.35" customHeight="1">
-      <c r="A117" s="4"/>
-      <c r="B117" s="28">
-        <v>1</v>
-      </c>
-      <c r="C117" s="29">
-        <v>100</v>
-      </c>
-      <c r="D117" s="30"/>
-      <c r="E117" s="7"/>
-    </row>
-    <row r="118" ht="15.35" customHeight="1">
-      <c r="A118" s="4"/>
-      <c r="B118" s="28">
-        <v>2</v>
-      </c>
-      <c r="C118" s="29">
-        <v>200</v>
-      </c>
-      <c r="D118" s="30"/>
-      <c r="E118" s="7"/>
-    </row>
-    <row r="119" ht="15.35" customHeight="1">
-      <c r="A119" s="4"/>
-      <c r="B119" s="28">
-        <v>3</v>
-      </c>
-      <c r="C119" s="28">
-        <v>300</v>
-      </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B105:B112"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B100:B106"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C108:D108"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
